--- a/data/Testcase.xlsx
+++ b/data/Testcase.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://microsoftapc-my.sharepoint.com/personal/v-avishwanat_microsoft_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C82F63D-4699-4C30-A165-371FFE527CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{6C82F63D-4699-4C30-A165-371FFE527CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E71F04A-3BEF-4E3C-AFDE-6D4171B2EDEE}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3F262E1A-A868-4F20-9F0A-93B40355D21A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3F262E1A-A868-4F20-9F0A-93B40355D21A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Login" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>test_case</t>
   </si>
@@ -59,9 +59,6 @@
     <t>valid_user@test.com</t>
   </si>
   <si>
-    <t>Test@123</t>
-  </si>
-  <si>
     <t>passed</t>
   </si>
   <si>
@@ -71,17 +68,23 @@
     <t>Wrong@123</t>
   </si>
   <si>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>abhiachar86@gmail.com</t>
+  </si>
+  <si>
+    <t>Abhi@1234</t>
+  </si>
+  <si>
     <t>failed</t>
-  </si>
-  <si>
-    <t>NULL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,6 +104,14 @@
       <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -152,10 +163,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -163,11 +175,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -181,6 +197,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -507,7 +527,7 @@
     <col min="2" max="2" width="29.36328125" customWidth="1"/>
     <col min="3" max="3" width="18.26953125" customWidth="1"/>
     <col min="4" max="4" width="19.1796875" customWidth="1"/>
-    <col min="5" max="5" width="21.54296875" customWidth="1"/>
+    <col min="5" max="5" width="34.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -531,37 +551,47 @@
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{C286A80E-FCB3-44BC-83F0-504402401A04}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{3561818B-5488-4F15-9E67-47354DA697F1}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{f42aa342-8706-4288-bd11-ebb85995028c}" enabled="1" method="Standard" siteId="{72f988bf-86f1-41af-91ab-2d7cd011db47}" removed="0"/>
+</clbl:labelList>
 </file>